--- a/results/assessment/vIAbility/features/markers/ML/iter5/cv_results.xlsx
+++ b/results/assessment/vIAbility/features/markers/ML/iter5/cv_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -558,646 +558,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5039</v>
+        <v>0.462</v>
       </c>
       <c r="C3" t="n">
-        <v>0.372</v>
+        <v>0.3657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3507</v>
+        <v>0.4859</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3587</v>
+        <v>0.3829</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3491</v>
+        <v>0.4138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4504</v>
+        <v>0.4442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0482</v>
+        <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0646</v>
+        <v>0.059</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1563</v>
+        <v>0.1554</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0776</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1066</v>
+        <v>0.0959</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0456</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4935</v>
+        <v>0.5039</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3826</v>
+        <v>0.372</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3848</v>
+        <v>0.3507</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3817</v>
+        <v>0.3587</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3816</v>
+        <v>0.3491</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4634</v>
+        <v>0.4504</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0745</v>
+        <v>0.0482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0646</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.1563</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0713</v>
+        <v>0.0776</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0639</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLPClassifier</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4062</v>
+        <v>0.4935</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4062</v>
+        <v>0.3826</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.3848</v>
       </c>
       <c r="E5" t="n">
-        <v>0.461</v>
+        <v>0.3817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5777</v>
+        <v>0.3816</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5014</v>
+        <v>0.4634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0067</v>
+        <v>0.0745</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0067</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0069</v>
+        <v>0.0713</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0712</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>MLPClassifier</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5283</v>
+        <v>0.4062</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3646</v>
+        <v>0.4062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1801</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2989</v>
+        <v>0.461</v>
       </c>
       <c r="F6" t="n">
-        <v>0.238</v>
+        <v>0.5777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4422</v>
+        <v>0.5014</v>
       </c>
       <c r="H6" t="n">
-        <v>0.067</v>
+        <v>0.0067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1407</v>
+        <v>0.0067</v>
       </c>
       <c r="J6" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1007</v>
+        <v>0.0069</v>
       </c>
       <c r="L6" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.0712</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.0449</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TabPFN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5696</v>
+        <v>0.5283</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2338</v>
+        <v>0.3646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0851</v>
+        <v>0.1801</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1716</v>
+        <v>0.2989</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1238</v>
+        <v>0.238</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4555</v>
+        <v>0.4422</v>
       </c>
       <c r="H7" t="n">
-        <v>0.017</v>
+        <v>0.067</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1993</v>
+        <v>0.1407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1503</v>
+        <v>0.1007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.112</v>
+        <v>0.0712</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0533</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bagging_RandomForest</t>
+          <t>TabPFN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5696</v>
       </c>
       <c r="C8" t="n">
-        <v>0.396</v>
+        <v>0.2338</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3257</v>
+        <v>0.0851</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3771</v>
+        <v>0.1716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3543</v>
+        <v>0.1238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4588</v>
+        <v>0.4555</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0645</v>
+        <v>0.1993</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0565</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0563</v>
+        <v>0.1503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0528</v>
+        <v>0.112</v>
       </c>
       <c r="M8" t="n">
-        <v>0.062</v>
+        <v>0.0533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bagging_SVC</t>
+          <t>Bagging_RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4691</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3566</v>
+        <v>0.396</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3924</v>
+        <v>0.3257</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3604</v>
+        <v>0.3771</v>
       </c>
       <c r="F9" t="n">
-        <v>0.369</v>
+        <v>0.3543</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4592</v>
+        <v>0.4588</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0511</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0558</v>
+        <v>0.0645</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1129</v>
+        <v>0.0565</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0623</v>
+        <v>0.0563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0764</v>
+        <v>0.0528</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0638</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bagging_GaussianNB</t>
+          <t>Bagging_SVC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4934</v>
+        <v>0.4691</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3607</v>
+        <v>0.3566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3167</v>
+        <v>0.3924</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3427</v>
+        <v>0.3604</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3265</v>
+        <v>0.369</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4656</v>
+        <v>0.4592</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0552</v>
+        <v>0.0511</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0491</v>
+        <v>0.0558</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1171</v>
+        <v>0.1129</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0545</v>
+        <v>0.0623</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0404</v>
+        <v>0.0638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging_DecisionTree</t>
+          <t>Bagging_GaussianNB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5001</v>
+        <v>0.4934</v>
       </c>
       <c r="C11" t="n">
-        <v>0.338</v>
+        <v>0.3607</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2486</v>
+        <v>0.3167</v>
       </c>
       <c r="E11" t="n">
-        <v>0.312</v>
+        <v>0.3427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2828</v>
+        <v>0.3265</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4296</v>
+        <v>0.4656</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0226</v>
+        <v>0.0552</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0326</v>
+        <v>0.0491</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0711</v>
+        <v>0.1171</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0434</v>
+        <v>0.0545</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0576</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0723</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging_MLPClassifier</t>
+          <t>Bagging_DecisionTree</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5627</v>
+        <v>0.5001</v>
       </c>
       <c r="C12" t="n">
-        <v>0.19</v>
+        <v>0.338</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0341</v>
+        <v>0.2486</v>
       </c>
       <c r="E12" t="n">
-        <v>0.099</v>
+        <v>0.312</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0577</v>
+        <v>0.2828</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4973</v>
+        <v>0.4296</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0221</v>
+        <v>0.0226</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1855</v>
+        <v>0.0326</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0324</v>
+        <v>0.0711</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0434</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0551</v>
+        <v>0.0576</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0791</v>
+        <v>0.0723</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bagging_LogisticRegression</t>
+          <t>Bagging_MLPClassifier</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.518</v>
+        <v>0.5627</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3427</v>
+        <v>0.19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1793</v>
+        <v>0.0341</v>
       </c>
       <c r="E13" t="n">
-        <v>0.284</v>
+        <v>0.099</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2301</v>
+        <v>0.0577</v>
       </c>
       <c r="G13" t="n">
-        <v>0.454</v>
+        <v>0.4973</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0751</v>
+        <v>0.0221</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1662</v>
+        <v>0.1855</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0861</v>
+        <v>0.0324</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1288</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1023</v>
+        <v>0.0551</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0491</v>
+        <v>0.0791</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bagging_TabPFN</t>
+          <t>Bagging_LogisticRegression</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5558</v>
+        <v>0.518</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2667</v>
+        <v>0.3427</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0598</v>
+        <v>0.1793</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1497</v>
+        <v>0.284</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.2301</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4027</v>
+        <v>0.454</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0309</v>
+        <v>0.0751</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2494</v>
+        <v>0.1662</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0508</v>
+        <v>0.0861</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1244</v>
+        <v>0.1288</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0786</v>
+        <v>0.1023</v>
       </c>
       <c r="M14" t="n">
-        <v>0.029</v>
+        <v>0.0491</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Voting_soft_GaussianNB+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
+          <t>Bagging_TabPFN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4587</v>
+        <v>0.5558</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3679</v>
+        <v>0.2667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4873</v>
+        <v>0.0598</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3856</v>
+        <v>0.1497</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4167</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4436</v>
+        <v>0.4027</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0658</v>
+        <v>0.0309</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06</v>
+        <v>0.2494</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1414</v>
+        <v>0.0508</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0696</v>
+        <v>0.1244</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0891</v>
+        <v>0.0786</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0764</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3612</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4707</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3778</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4068</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.4636</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0788</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0699</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1389</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.07770000000000001</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0742</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.4449</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.3641</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.5047</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.3848</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4215</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.4588</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0536</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1224</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0609</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0765</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0843</v>
+        <v>0.029</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1608,156 +1522,6 @@
       </c>
       <c r="G15" t="n">
         <v>0.6213</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2941</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2373</v>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_hard_MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.2941</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.2373</v>
-      </c>
-      <c r="G17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Voting_hard_SVC+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.2941</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.2373</v>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Voting_soft_GaussianNB+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.5934</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5192</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.6923</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5466</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5934</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.6109</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5618</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5981</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4821</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.6923</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.5133</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5684</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5976</v>
       </c>
     </row>
   </sheetData>
